--- a/sample_data/function_master.xlsx
+++ b/sample_data/function_master.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>機能概要</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -500,6 +505,11 @@
           <t>User Login</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>メールアドレスとパスワードでログイン認証を行う。失敗回数のロックアウト、SAML/OIDC連携、二要素認証(TOTP)に対応。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -535,6 +545,11 @@
           <t>User Registration</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>新規ユーザー登録フォーム。メール検証トークンの送付・有効化、利用規約同意の記録、reCAPTCHA連携を含む。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -570,6 +585,11 @@
           <t>Password Reset</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>パスワード忘却時の再設定フロー。本人確認メール経由のワンタイムリンクと、24時間の有効期限管理を行う。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -605,6 +625,11 @@
           <t>Profile Edit</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ユーザー本人によるプロフィール編集。表示名、アイコン、通知設定、タイムゾーンを更新できる。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -640,6 +665,11 @@
           <t>Profile Edit (Admin)</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>管理者によるプロフィール編集。所属、権限ロール、停止/復活フラグなど一般ユーザーには触れない項目を含む。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -682,6 +712,11 @@
           <t>Search (Basic)</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>全文検索の基本機能。商品名・説明文に対するキーワードマッチと、件数ベースのページング表示を提供する。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -717,6 +752,11 @@
           <t>Search (Advanced)</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>高度な検索フィルタ。価格帯・在庫状況・カテゴリ・タグの複合条件と、ファセットUIによる絞り込みに対応。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -752,6 +792,11 @@
           <t>Cart Add</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>カートへの商品追加。在庫引当はせず、購入確定時に再検証する楽観方式。SKU単位で数量管理する。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -787,6 +832,11 @@
           <t>Cart Remove</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>カートからの商品削除と数量変更。削除取り消しのスナックバーUIをWebフロントで提供する。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -822,6 +872,11 @@
           <t>Checkout</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>チェックアウトフロー。配送先・支払い方法・クーポン適用・合計金額の確認を経て注文を確定する。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -864,6 +919,11 @@
           <t>Payment - Credit Card</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>クレジットカード決済。3DS2.0認証、決済代行APIとの連携、決済失敗時のリトライポリシーを持つ。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -899,6 +959,11 @@
           <t>Payment - Bank Transfer</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>銀行振込決済。仮想口座番号の自動採番、入金照合バッチ、未入金リマインダ送信を含む。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -934,6 +999,11 @@
           <t>Order History</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ユーザー自身の過去注文一覧。直近24ヶ月分を表示し、領収書PDFダウンロードに対応する。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -969,6 +1039,11 @@
           <t>Notification - Email</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>メール通知の送信機能。テンプレート展開、配信ステータス追跡、バウンス処理を行う。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1004,6 +1079,11 @@
           <t>Notification - Push</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>プッシュ通知。FCM/APNs両対応、ユーザーごとの通知許可設定とサイレント時間帯の制御を行う。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1039,6 +1119,11 @@
           <t>Settings Sync</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>アプリ設定の端末間同期。差分マージとコンフリクト解決(最終更新優先)を実装する。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1074,6 +1159,11 @@
           <t>Data Export</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>データエクスポート機能。CSV/Excel形式での出力と、大量データ時の非同期ジョブ化に対応。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1109,6 +1199,11 @@
           <t>Data Import</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>データインポート機能。CSVフォーマットの検証、エラー行のレポート、ロールバック処理を含む。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1145,6 +1240,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="n"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>監査ログ。重要操作の不可変ログ記録と、検索・フィルタ・CSV出力UIを提供する。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1178,6 +1278,11 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>Admin Dashboard</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>管理者向けダッシュボード。利用状況・障害アラート・リクエスト数の主要KPIを集約表示する。</t>
         </is>
       </c>
     </row>

--- a/sample_data/function_master.xlsx
+++ b/sample_data/function_master.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,11 +465,6 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>機能概要</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -505,11 +500,6 @@
           <t>User Login</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>メールアドレスとパスワードでログイン認証を行う。失敗回数のロックアウト、SAML/OIDC連携、二要素認証(TOTP)に対応。</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -545,11 +535,6 @@
           <t>User Registration</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>新規ユーザー登録フォーム。メール検証トークンの送付・有効化、利用規約同意の記録、reCAPTCHA連携を含む。</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,11 +570,6 @@
           <t>Password Reset</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>パスワード忘却時の再設定フロー。本人確認メール経由のワンタイムリンクと、24時間の有効期限管理を行う。</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -622,12 +602,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Profile Edit</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ユーザー本人によるプロフィール編集。表示名、アイコン、通知設定、タイムゾーンを更新できる。</t>
+          <t>Profile Edit (旧仕様 — 上書き対象)</t>
         </is>
       </c>
     </row>
@@ -665,11 +640,6 @@
           <t>Profile Edit (Admin)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>管理者によるプロフィール編集。所属、権限ロール、停止/復活フラグなど一般ユーザーには触れない項目を含む。</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -709,12 +679,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Search (Basic)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>全文検索の基本機能。商品名・説明文に対するキーワードマッチと、件数ベースのページング表示を提供する。</t>
+          <t>Search (Basic 旧仕様 — 上書き対象)</t>
         </is>
       </c>
     </row>
@@ -749,12 +714,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Search (Advanced)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>高度な検索フィルタ。価格帯・在庫状況・カテゴリ・タグの複合条件と、ファセットUIによる絞り込みに対応。</t>
+          <t>Search (Advanced 新仕様 — 採用される)</t>
         </is>
       </c>
     </row>
@@ -792,11 +752,6 @@
           <t>Cart Add</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>カートへの商品追加。在庫引当はせず、購入確定時に再検証する楽観方式。SKU単位で数量管理する。</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -832,11 +787,6 @@
           <t>Cart Remove</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>カートからの商品削除と数量変更。削除取り消しのスナックバーUIをWebフロントで提供する。</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -872,11 +822,6 @@
           <t>Checkout</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>チェックアウトフロー。配送先・支払い方法・クーポン適用・合計金額の確認を経て注文を確定する。</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -916,12 +861,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Payment - Credit Card</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>クレジットカード決済。3DS2.0認証、決済代行APIとの連携、決済失敗時のリトライポリシーを持つ。</t>
+          <t>Payment - Credit Card (旧仕様 — 上書き対象)</t>
         </is>
       </c>
     </row>
@@ -956,12 +896,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Payment - Bank Transfer</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>銀行振込決済。仮想口座番号の自動採番、入金照合バッチ、未入金リマインダ送信を含む。</t>
+          <t>Payment - Bank Transfer (新仕様 — 採用される)</t>
         </is>
       </c>
     </row>
@@ -999,11 +934,6 @@
           <t>Order History</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>ユーザー自身の過去注文一覧。直近24ヶ月分を表示し、領収書PDFダウンロードに対応する。</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1039,11 +969,6 @@
           <t>Notification - Email</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>メール通知の送信機能。テンプレート展開、配信ステータス追跡、バウンス処理を行う。</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1079,11 +1004,6 @@
           <t>Notification - Push</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>プッシュ通知。FCM/APNs両対応、ユーザーごとの通知許可設定とサイレント時間帯の制御を行う。</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,11 +1039,6 @@
           <t>Settings Sync</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>アプリ設定の端末間同期。差分マージとコンフリクト解決(最終更新優先)を実装する。</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1159,11 +1074,6 @@
           <t>Data Export</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>データエクスポート機能。CSV/Excel形式での出力と、大量データ時の非同期ジョブ化に対応。</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1191,103 +1101,123 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>USER010</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Profile Edit (新仕様 — 採用される)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bob</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>IMP001</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Data Import</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>データインポート機能。CSVフォーマットの検証、エラー行のレポート、ロールバック処理を含む。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Worker</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>bob</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>carol</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>AUDIT01</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Audit Log</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>監査ログ。重要操作の不可変ログ記録と、検索・フィルタ・CSV出力UIを提供する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>carol</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>alice</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>ADM001</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Admin Dashboard</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>管理者向けダッシュボード。利用状況・障害アラート・リクエスト数の主要KPIを集約表示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
